--- a/static/standards-correlations/Rhode_Island_CS1_State_Standards.xlsx
+++ b/static/standards-correlations/Rhode_Island_CS1_State_Standards.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Crosswalk'!$A$4:$I$38</definedName>
@@ -550,10 +550,11 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scored against full lab bodies | C and Python tracks | Discovery Projects | RI CS Education Standards, May 2018 | Single 9-12 band, six concepts</t>
-        </is>
-      </c>
-    </row>
+          <t>Scored against full lab bodies | C and Python tracks | Introductory Projects | RI CS Education Standards, May 2018 | Single 9-12 band, six concepts</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -587,7 +588,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Discovery Projects</t>
+          <t>Introductory Projects</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -1470,7 +1471,7 @@
       </c>
       <c r="I23" s="8" t="inlineStr">
         <is>
-          <t>Discovery Systems 10 covers recognising and not acting on a phishing attempt. Breach response, evidence gathering and reporting protocols are not addressed.</t>
+          <t>Introductory Systems 10 covers recognising and not acting on a phishing attempt. Breach response, evidence gathering and reporting protocols are not addressed.</t>
         </is>
       </c>
     </row>
@@ -2173,6 +2174,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
@@ -2217,7 +2219,7 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>Discovery Project, Coding strand, project NN (01-17).</t>
+          <t>Introductory Project, Coding strand, project NN (01-17).</t>
         </is>
       </c>
     </row>
@@ -2229,7 +2231,7 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Discovery Project, Systems strand, project NN (01-14).</t>
+          <t>Introductory Project, Systems strand, project NN (01-14).</t>
         </is>
       </c>
     </row>
@@ -2341,6 +2343,8 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
@@ -2369,7 +2373,7 @@
 CSTA LICENCE NOTE: Rhode Island records that the CSTA standards it adapted are licensed CC BY-NC-SA 4.0. Rhode Island's own document is the source used here.
 Crosswalk analysis (c) KIPR / Botball Explorer.
 === METHODOLOGY (revised) ===
-Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Discovery projects.
+Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Introductory projects.
 Scoring rule: Full requires evidence in the core lab flow. Partial is assigned where the only evidence sits in an optional Extension Challenge (labelled 'Finished early?'), or where the standard is only partly met. Rhode Island publishes an extended description for each standard in Appendix A; those descriptions were used to judge intent and are cited in Coverage notes where they changed the score.</t>
         </is>
       </c>
